--- a/hp-tracker-template.xlsx
+++ b/hp-tracker-template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mreillyorg\iCloudDrive\iCloud~md~obsidian\mreillyorg - dnd - al chars\dm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mreillyorg\iCloudDrive\iCloud~md~obsidian\mreillyorg - dnd - al chars\dm\dnd-hp-tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7C9202C-A838-43B3-87ED-6D360C72DE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B3F205D-E660-4157-A8FC-04BB20B13A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="2" xr2:uid="{B7F0EF5F-C82E-4619-967A-0DA36F0C153E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{B7F0EF5F-C82E-4619-967A-0DA36F0C153E}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="1" r:id="rId1"/>
@@ -197,9 +197,6 @@
     <t>Very thin goo</t>
   </si>
   <si>
-    <t>Michael Reilly's D&amp;D Combat Encounter Tracker version 1.1</t>
-  </si>
-  <si>
     <t>Leave 'Config' sheet alone</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Michael Reilly's D&amp;D Combat Encounter Tracker version 1.2</t>
   </si>
 </sst>
 </file>
@@ -726,7 +726,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -756,7 +756,7 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -7828,7 +7828,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -7845,7 +7845,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
@@ -16081,7 +16081,7 @@
         <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H1" t="s">
         <v>27</v>
